--- a/assets_cropped/Symboli Rudolf/transformed/manifest_edit.xlsx
+++ b/assets_cropped/Symboli Rudolf/transformed/manifest_edit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\TanukiProject\tanuki_app\assets_cropped\Symboli Rudolf\transformed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64646E18-3D17-4880-97DC-73214D947ECB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39770291-29BA-4A9E-991B-BD4BE56E559D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="8955" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="85">
   <si>
     <t>filename</t>
   </si>
@@ -261,10 +261,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>relation_watch,random,window_perch,activity_race_recovery</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>random,window_perch,activity_race_challenge</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -285,7 +281,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>care_companion,observe_hold,activity_race_consider</t>
+    <t>care_companion,observe_hold,activity_race_consider,activity_chorus_finish</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>relation_watch,random,window_perch,activity_race_recovery,activity_chorus_observe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>random,window_walk,activity_chorus_approach</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>random,window_walk,activity_race_to_start,activity_chorus_approach</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>activity_chorus_perform</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +667,7 @@
         <v>62</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -677,13 +689,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -697,7 +709,7 @@
         <v>62</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -705,13 +717,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -725,7 +737,7 @@
         <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -756,7 +768,7 @@
         <v>62</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -784,7 +796,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -798,7 +810,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -826,7 +838,7 @@
         <v>62</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -983,7 +995,7 @@
         <v>62</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -997,7 +1009,7 @@
         <v>62</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D28">
         <v>1</v>
